--- a/splists_out/needs_revision/zotz_species_not_in_garwood.xlsx
+++ b/splists_out/needs_revision/zotz_species_not_in_garwood.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AV11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -392,205 +392,225 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>NewName</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>NewAuthority</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DateChange</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>orig_author</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>orig_family</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>orig_name</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>orig_author</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>orig_genus</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>orig_species</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>orig_infraspecies_rank</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>orig_infraspecies</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>orig_binomial</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>wcvp_matched_name</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>wcvp_matched_authors</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>wcvp_matched_rank</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>wcvp_matched_status</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>wcvp_matched_plant_name_id</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>wcvp_matched_ipni_id</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>match_similarity</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_plant_name_id</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_powo_id</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_ipni_id</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_name</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_name_genus</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_name_species</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_name_rank</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_family</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_name_infraspecific_rank</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_name_infraspecies</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_author</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_authority</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_lifeform</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>origmatches</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>wcvp_accepted_binomial</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>wcvp_matched_binomial</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>croat_name</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>croat_binomial</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>matchorig</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>matchcroat</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>matchorigsynonym</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>matchcroatsynonym</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>matchwcvpmatch</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>matchwcvpaccept</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>matchany</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>firstmatchtype</t>
         </is>
@@ -622,153 +642,141 @@
           <t>[Croat 6281]</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Polypodiaceae</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Campyloneurum angustifolium</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Campyloneurum</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>angustifolium</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Campyloneurum angustifolium</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Campyloneurum angustifolium</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>(Sw.) Fée</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>3154609</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>17063000-1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>3154609</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>17063000-1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>17063000-1</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Campyloneurum angustifolium</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Campyloneurum</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>angustifolium</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Polypodiaceae</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>Fée</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>(Sw.) Fée</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>epiphyte</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>Campyloneurum angustifolium</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Campyloneurum angustifolium</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="AO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="b">
-        <v>0</v>
-      </c>
       <c r="AS2" t="b">
         <v>0</v>
       </c>
@@ -776,6 +784,18 @@
         <v>0</v>
       </c>
       <c r="AU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -805,153 +825,141 @@
           <t>Einzmann et al. (2015)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Dryopteridaceae</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Elaphoglossum doanense</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Elaphoglossum</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>doanense</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Elaphoglossum doanense</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Elaphoglossum doanense</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>L.D.Gómez</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>3152014</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>17437440-1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>3152014</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>17437440-1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>17437440-1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Elaphoglossum doanense</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Elaphoglossum</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>doanense</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>Polypodiaceae</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>L.D.Gómez</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>L.D.Gómez</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>epiphyte</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>Elaphoglossum doanense</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>Elaphoglossum doanense</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="AO3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="b">
-        <v>0</v>
-      </c>
       <c r="AS3" t="b">
         <v>0</v>
       </c>
@@ -959,6 +967,18 @@
         <v>0</v>
       </c>
       <c r="AU3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -988,153 +1008,141 @@
           <t>Einzmann et al. (2015)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Dryopteridaceae</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Elaphoglossum latum</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Elaphoglossum</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>latum</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Elaphoglossum latum</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Elaphoglossum latum</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>(Mickel) Mickel</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>3152132</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>1191316-2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>3152132</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>1191316-2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1191316-2</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Elaphoglossum latum</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Elaphoglossum</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>latum</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>Polypodiaceae</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>Mickel</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>(Mickel) Mickel</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>epiphyte</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>Elaphoglossum latum</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>Elaphoglossum latum</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="AO4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="b">
-        <v>0</v>
-      </c>
       <c r="AS4" t="b">
         <v>0</v>
       </c>
@@ -1142,6 +1150,18 @@
         <v>0</v>
       </c>
       <c r="AU4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1171,153 +1191,141 @@
           <t>Einzmann et al. (2015)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Dryopteridaceae</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Elaphoglossum peltatum</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Elaphoglossum</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>peltatum</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Elaphoglossum peltatum</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Elaphoglossum peltatum</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>(Sw.) Urb.</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>3152314</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>89267-2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>3152314</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>89267-2</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>89267-2</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Elaphoglossum peltatum</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Elaphoglossum</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>peltatum</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>Polypodiaceae</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>Urb.</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>(Sw.) Urb.</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>epiphyte</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>Elaphoglossum peltatum</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>Elaphoglossum peltatum</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="AO5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="b">
-        <v>0</v>
-      </c>
       <c r="AS5" t="b">
         <v>0</v>
       </c>
@@ -1325,6 +1333,18 @@
         <v>0</v>
       </c>
       <c r="AU5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1359,153 +1379,141 @@
           <t>[Croat 10106]</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Orchidaceae</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Epidendrum umbilliferum</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Epidendrum</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>umbilliferum</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Epidendrum umbilliferum</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Epidendrum umbelliferum</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>J.F.Gmel.</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>69800</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>632948-1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.957</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>69800</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>632948-1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>632948-1</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Epidendrum umbelliferum</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Epidendrum</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>umbelliferum</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>Orchidaceae</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>J.F.Gmel.</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>J.F.Gmel.</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>epiphyte</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>Epidendrum umbelliferum</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>Epidendrum umbelliferum</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="AO6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="b">
-        <v>0</v>
-      </c>
       <c r="AS6" t="b">
         <v>0</v>
       </c>
@@ -1513,6 +1521,18 @@
         <v>0</v>
       </c>
       <c r="AU6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1542,153 +1562,141 @@
           <t>Einzmann et al. (2015)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Orchidaceae</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Maxillariella acervata</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Maxillariella</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>acervata</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Maxillariella acervata</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Maxillariella acervata</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>(Rchb.f.) M.A.Blanco &amp; Carnevali</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Synonym</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>374874</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>60448161-2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>122277</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>318683-2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>318683-2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Maxillaria acervata</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Maxillaria</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>acervata</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>Orchidaceae</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>Rchb.f.</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>Rchb.f.</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>pseudobulbous epiphyte</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Maxillaria acervata</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>Maxillariella acervata</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="AO7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="b">
-        <v>0</v>
-      </c>
       <c r="AS7" t="b">
         <v>0</v>
       </c>
@@ -1696,6 +1704,18 @@
         <v>0</v>
       </c>
       <c r="AU7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1725,153 +1745,141 @@
           <t>[Schmalzel 1406]</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Piperaceae</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Peperomia elata</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Peperomia</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>elata</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Peperomia elata</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Peperomia elata</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>C.DC.</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>2557311</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>188675-2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>2557311</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>188675-2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>188675-2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Peperomia elata</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Peperomia</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>elata</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>Piperaceae</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>C.DC.</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>C.DC.</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>epiphyte or lithophyte</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Peperomia elata</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>Peperomia elata</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="AO8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="b">
-        <v>0</v>
-      </c>
       <c r="AS8" t="b">
         <v>0</v>
       </c>
@@ -1879,6 +1887,18 @@
         <v>0</v>
       </c>
       <c r="AU8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1908,153 +1928,141 @@
           <t>[Croat 8055]</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Piperaceae</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Peperomia portobellensis</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Peperomia</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>portobellensis</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Peperomia portobellensis</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Peperomia portobellensis</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Beurl.</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>2556055</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>679487-1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>2556055</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>679487-1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>679487-1</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Peperomia portobellensis</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>Peperomia</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>portobellensis</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>Piperaceae</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>Beurl.</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>Beurl.</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>epiphyte or lithophyte</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Peperomia portobellensis</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>Peperomia portobellensis</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="AO9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="b">
-        <v>0</v>
-      </c>
       <c r="AS9" t="b">
         <v>0</v>
       </c>
@@ -2062,6 +2070,18 @@
         <v>0</v>
       </c>
       <c r="AU9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2091,153 +2111,141 @@
           <t>[Ebinger 231]</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Polypodiaceae</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Pleopeltis panamensis</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Pleopeltis</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>panamensis</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>Pleopeltis panamensis</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Pleopeltis panamensis</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>(Weath.) Pic.Serm.</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>3154902</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>202103-2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>3154902</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>202103-2</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>202103-2</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Pleopeltis panamensis</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>Pleopeltis</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>panamensis</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>Polypodiaceae</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>Pic.Serm.</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>(Weath.) Pic.Serm.</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>epiphyte</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>Pleopeltis panamensis</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>Pleopeltis panamensis</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="AO10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="b">
-        <v>0</v>
-      </c>
       <c r="AS10" t="b">
         <v>0</v>
       </c>
@@ -2245,6 +2253,18 @@
         <v>0</v>
       </c>
       <c r="AU10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2274,153 +2294,141 @@
           <t>[Foster s.n.]</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Orchidaceae</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Prosthechea aemula</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Prosthechea</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>aemula</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Prosthechea aemula</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Prosthechea aemula</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>(Lindl.) W.E.Higgins</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>165791</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>1001227-1</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>165791</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>1001227-1</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1001227-1</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>Prosthechea aemula</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>Prosthechea</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>aemula</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>Orchidaceae</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>W.E.Higgins</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>(Lindl.) W.E.Higgins</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>pseudobulbous epiphyte</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>Prosthechea aemula</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>Prosthechea aemula</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="AO11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="b">
-        <v>0</v>
-      </c>
       <c r="AS11" t="b">
         <v>0</v>
       </c>
@@ -2428,6 +2436,18 @@
         <v>0</v>
       </c>
       <c r="AU11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="b">
         <v>0</v>
       </c>
     </row>
